--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.36534278040772</v>
+        <v>9.484368201816254</v>
       </c>
       <c r="D2" t="n">
-        <v>58.15770709749217</v>
+        <v>9.450627403342478</v>
       </c>
       <c r="E2" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F2" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.02222420479366</v>
+        <v>8.77861143327897</v>
       </c>
       <c r="D3" t="n">
-        <v>54.03012006522258</v>
+        <v>8.77989451059867</v>
       </c>
       <c r="E3" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F3" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.42361382278784</v>
+        <v>3.643837246203025</v>
       </c>
       <c r="D4" t="n">
-        <v>22.26961513170778</v>
+        <v>3.618812458902514</v>
       </c>
       <c r="E4" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F4" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.01637866483835</v>
+        <v>4.715161533036231</v>
       </c>
       <c r="D5" t="n">
-        <v>28.79633666359306</v>
+        <v>4.679404707833873</v>
       </c>
       <c r="E5" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F5" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.10392466216861</v>
+        <v>6.029387757602399</v>
       </c>
       <c r="D6" t="n">
-        <v>37.11131011850943</v>
+        <v>6.030587894257782</v>
       </c>
       <c r="E6" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F6" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.71026267129565</v>
+        <v>7.590417684085542</v>
       </c>
       <c r="D7" t="n">
-        <v>46.531906389413</v>
+        <v>7.561434788279613</v>
       </c>
       <c r="E7" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F7" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86489140300871</v>
+        <v>3.715544852988915</v>
       </c>
       <c r="D8" t="n">
-        <v>22.9624686208353</v>
+        <v>3.731401150885736</v>
       </c>
       <c r="E8" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F8" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.817088232862103</v>
+        <v>1.595276837840092</v>
       </c>
       <c r="D9" t="n">
-        <v>9.61570528899847</v>
+        <v>1.562552109462251</v>
       </c>
       <c r="E9" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F9" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.03745595460741</v>
+        <v>7.643586592623704</v>
       </c>
       <c r="D10" t="n">
-        <v>46.90273709636355</v>
+        <v>7.621694778159077</v>
       </c>
       <c r="E10" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F10" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.55174865075062</v>
+        <v>3.827159155746977</v>
       </c>
       <c r="D11" t="n">
-        <v>23.46966535677269</v>
+        <v>3.813820620475562</v>
       </c>
       <c r="E11" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F11" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.00911001752268</v>
+        <v>4.713980377847435</v>
       </c>
       <c r="D12" t="n">
-        <v>29.22266895123465</v>
+        <v>4.74868370457563</v>
       </c>
       <c r="E12" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F12" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.28008552821087</v>
+        <v>7.683013898334266</v>
       </c>
       <c r="D13" t="n">
-        <v>47.31258725011146</v>
+        <v>7.688295428143113</v>
       </c>
       <c r="E13" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F13" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.32362994162818</v>
+        <v>6.390089865514579</v>
       </c>
       <c r="D14" t="n">
-        <v>39.40986808653774</v>
+        <v>6.404103564062384</v>
       </c>
       <c r="E14" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F14" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.29723002862281</v>
+        <v>5.735799879651207</v>
       </c>
       <c r="D15" t="n">
-        <v>35.48166949682184</v>
+        <v>5.765771293233549</v>
       </c>
       <c r="E15" t="n">
-        <v>13.35290716335564</v>
+        <v>2.169847414045291</v>
       </c>
       <c r="F15" t="n">
-        <v>13.35204844830022</v>
+        <v>2.169707872848786</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
